--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500761</v>
+        <v>121500891</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>94588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562721</v>
+        <v>562753</v>
       </c>
       <c r="R2" t="n">
-        <v>6515236</v>
+        <v>6515193</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501352</v>
+        <v>121501361</v>
       </c>
       <c r="B3" t="n">
-        <v>94588</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6515178</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500891</v>
+        <v>121500761</v>
       </c>
       <c r="B4" t="n">
-        <v>94588</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562753</v>
+        <v>562721</v>
       </c>
       <c r="R4" t="n">
-        <v>6515193</v>
+        <v>6515236</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501108</v>
+        <v>121501039</v>
       </c>
       <c r="B5" t="n">
-        <v>94588</v>
+        <v>91263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562821</v>
+        <v>562804</v>
       </c>
       <c r="R5" t="n">
-        <v>6515227</v>
+        <v>6515197</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121501361</v>
+        <v>121501352</v>
       </c>
       <c r="B6" t="n">
-        <v>100364</v>
+        <v>94588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
         <v>6515178</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501039</v>
+        <v>121501108</v>
       </c>
       <c r="B7" t="n">
-        <v>91263</v>
+        <v>94588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562804</v>
+        <v>562821</v>
       </c>
       <c r="R7" t="n">
-        <v>6515197</v>
+        <v>6515227</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121500891</v>
+        <v>121501039</v>
       </c>
       <c r="B2" t="n">
-        <v>94588</v>
+        <v>91263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562753</v>
+        <v>562804</v>
       </c>
       <c r="R2" t="n">
-        <v>6515193</v>
+        <v>6515197</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501361</v>
+        <v>121501352</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>94588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6515178</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500761</v>
+        <v>121500891</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>94588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562721</v>
+        <v>562753</v>
       </c>
       <c r="R4" t="n">
-        <v>6515236</v>
+        <v>6515193</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501039</v>
+        <v>121501108</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>94588</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562804</v>
+        <v>562821</v>
       </c>
       <c r="R5" t="n">
-        <v>6515197</v>
+        <v>6515227</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121501352</v>
+        <v>121500761</v>
       </c>
       <c r="B6" t="n">
-        <v>94588</v>
+        <v>100364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         <v>562721</v>
       </c>
       <c r="R6" t="n">
-        <v>6515178</v>
+        <v>6515236</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501108</v>
+        <v>121501361</v>
       </c>
       <c r="B7" t="n">
-        <v>94588</v>
+        <v>100364</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562821</v>
+        <v>562721</v>
       </c>
       <c r="R7" t="n">
-        <v>6515227</v>
+        <v>6515178</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501039</v>
+        <v>121501108</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>94594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562804</v>
+        <v>562821</v>
       </c>
       <c r="R2" t="n">
-        <v>6515197</v>
+        <v>6515227</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501352</v>
+        <v>121501361</v>
       </c>
       <c r="B3" t="n">
-        <v>94588</v>
+        <v>100370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6515178</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121500891</v>
       </c>
       <c r="B4" t="n">
-        <v>94588</v>
+        <v>94594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501108</v>
+        <v>121500761</v>
       </c>
       <c r="B5" t="n">
-        <v>94588</v>
+        <v>100370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562821</v>
+        <v>562721</v>
       </c>
       <c r="R5" t="n">
-        <v>6515227</v>
+        <v>6515236</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500761</v>
+        <v>121501352</v>
       </c>
       <c r="B6" t="n">
-        <v>100364</v>
+        <v>94594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         <v>562721</v>
       </c>
       <c r="R6" t="n">
-        <v>6515236</v>
+        <v>6515178</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501361</v>
+        <v>121501039</v>
       </c>
       <c r="B7" t="n">
-        <v>100364</v>
+        <v>91269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562721</v>
+        <v>562804</v>
       </c>
       <c r="R7" t="n">
-        <v>6515178</v>
+        <v>6515197</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121501108</v>
       </c>
       <c r="B2" t="n">
-        <v>94594</v>
+        <v>94595</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121501361</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121500891</v>
       </c>
       <c r="B4" t="n">
-        <v>94594</v>
+        <v>94595</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500761</v>
+        <v>121501039</v>
       </c>
       <c r="B5" t="n">
-        <v>100370</v>
+        <v>91270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562721</v>
+        <v>562804</v>
       </c>
       <c r="R5" t="n">
-        <v>6515236</v>
+        <v>6515197</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1086,7 +1086,7 @@
         <v>121501352</v>
       </c>
       <c r="B6" t="n">
-        <v>94594</v>
+        <v>94595</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501039</v>
+        <v>121500761</v>
       </c>
       <c r="B7" t="n">
-        <v>91269</v>
+        <v>100371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562804</v>
+        <v>562721</v>
       </c>
       <c r="R7" t="n">
-        <v>6515197</v>
+        <v>6515236</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501108</v>
+        <v>121501361</v>
       </c>
       <c r="B2" t="n">
-        <v>94595</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562821</v>
+        <v>562721</v>
       </c>
       <c r="R2" t="n">
-        <v>6515227</v>
+        <v>6515178</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501361</v>
+        <v>121501039</v>
       </c>
       <c r="B3" t="n">
-        <v>100371</v>
+        <v>91270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562721</v>
+        <v>562804</v>
       </c>
       <c r="R3" t="n">
-        <v>6515178</v>
+        <v>6515197</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500891</v>
+        <v>121500761</v>
       </c>
       <c r="B4" t="n">
-        <v>94595</v>
+        <v>100371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562753</v>
+        <v>562721</v>
       </c>
       <c r="R4" t="n">
-        <v>6515193</v>
+        <v>6515236</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501039</v>
+        <v>121501108</v>
       </c>
       <c r="B5" t="n">
-        <v>91270</v>
+        <v>94595</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562804</v>
+        <v>562821</v>
       </c>
       <c r="R5" t="n">
-        <v>6515197</v>
+        <v>6515227</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500761</v>
+        <v>121500891</v>
       </c>
       <c r="B7" t="n">
-        <v>100371</v>
+        <v>94595</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562721</v>
+        <v>562753</v>
       </c>
       <c r="R7" t="n">
-        <v>6515236</v>
+        <v>6515193</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501361</v>
+        <v>121501352</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>94595</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>6515178</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501039</v>
+        <v>121501361</v>
       </c>
       <c r="B3" t="n">
-        <v>91270</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562804</v>
+        <v>562721</v>
       </c>
       <c r="R3" t="n">
-        <v>6515197</v>
+        <v>6515178</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501108</v>
+        <v>121500891</v>
       </c>
       <c r="B5" t="n">
         <v>94595</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562821</v>
+        <v>562753</v>
       </c>
       <c r="R5" t="n">
-        <v>6515227</v>
+        <v>6515193</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121501352</v>
+        <v>121501108</v>
       </c>
       <c r="B6" t="n">
         <v>94595</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562721</v>
+        <v>562821</v>
       </c>
       <c r="R6" t="n">
-        <v>6515178</v>
+        <v>6515227</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500891</v>
+        <v>121501039</v>
       </c>
       <c r="B7" t="n">
-        <v>94595</v>
+        <v>91270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562753</v>
+        <v>562804</v>
       </c>
       <c r="R7" t="n">
-        <v>6515193</v>
+        <v>6515197</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501352</v>
+        <v>121501361</v>
       </c>
       <c r="B2" t="n">
-        <v>94595</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>6515178</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501361</v>
+        <v>121500891</v>
       </c>
       <c r="B3" t="n">
-        <v>100371</v>
+        <v>94595</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562721</v>
+        <v>562753</v>
       </c>
       <c r="R3" t="n">
-        <v>6515178</v>
+        <v>6515193</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500761</v>
+        <v>121501039</v>
       </c>
       <c r="B4" t="n">
-        <v>100371</v>
+        <v>91270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562721</v>
+        <v>562804</v>
       </c>
       <c r="R4" t="n">
-        <v>6515236</v>
+        <v>6515197</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500891</v>
+        <v>121501352</v>
       </c>
       <c r="B5" t="n">
         <v>94595</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562753</v>
+        <v>562721</v>
       </c>
       <c r="R5" t="n">
-        <v>6515193</v>
+        <v>6515178</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501039</v>
+        <v>121500761</v>
       </c>
       <c r="B7" t="n">
-        <v>91270</v>
+        <v>100371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562804</v>
+        <v>562721</v>
       </c>
       <c r="R7" t="n">
-        <v>6515197</v>
+        <v>6515236</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121501361</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>100379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121500891</v>
       </c>
       <c r="B3" t="n">
-        <v>94595</v>
+        <v>94603</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121501039</v>
       </c>
       <c r="B4" t="n">
-        <v>91270</v>
+        <v>91278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>121501352</v>
       </c>
       <c r="B5" t="n">
-        <v>94595</v>
+        <v>94603</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>121501108</v>
       </c>
       <c r="B6" t="n">
-        <v>94595</v>
+        <v>94603</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>121500761</v>
       </c>
       <c r="B7" t="n">
-        <v>100371</v>
+        <v>100379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501361</v>
+        <v>121501108</v>
       </c>
       <c r="B2" t="n">
-        <v>100379</v>
+        <v>94603</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562721</v>
+        <v>562821</v>
       </c>
       <c r="R2" t="n">
-        <v>6515178</v>
+        <v>6515227</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501108</v>
+        <v>121501039</v>
       </c>
       <c r="B3" t="n">
-        <v>94603</v>
+        <v>91278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562821</v>
+        <v>562804</v>
       </c>
       <c r="R3" t="n">
-        <v>6515227</v>
+        <v>6515197</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121501352</v>
+        <v>121500891</v>
       </c>
       <c r="B4" t="n">
         <v>94603</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562721</v>
+        <v>562753</v>
       </c>
       <c r="R4" t="n">
-        <v>6515178</v>
+        <v>6515193</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121500891</v>
+        <v>121501352</v>
       </c>
       <c r="B5" t="n">
         <v>94603</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562753</v>
+        <v>562721</v>
       </c>
       <c r="R5" t="n">
-        <v>6515193</v>
+        <v>6515178</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501039</v>
+        <v>121501361</v>
       </c>
       <c r="B7" t="n">
-        <v>91278</v>
+        <v>100379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562804</v>
+        <v>562721</v>
       </c>
       <c r="R7" t="n">
-        <v>6515197</v>
+        <v>6515178</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501108</v>
+        <v>121500891</v>
       </c>
       <c r="B2" t="n">
         <v>94603</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562821</v>
+        <v>562753</v>
       </c>
       <c r="R2" t="n">
-        <v>6515227</v>
+        <v>6515193</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501039</v>
+        <v>121501352</v>
       </c>
       <c r="B3" t="n">
-        <v>91278</v>
+        <v>94603</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562804</v>
+        <v>562721</v>
       </c>
       <c r="R3" t="n">
-        <v>6515197</v>
+        <v>6515178</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500891</v>
+        <v>121501108</v>
       </c>
       <c r="B4" t="n">
         <v>94603</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562753</v>
+        <v>562821</v>
       </c>
       <c r="R4" t="n">
-        <v>6515193</v>
+        <v>6515227</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501352</v>
+        <v>121500761</v>
       </c>
       <c r="B5" t="n">
-        <v>94603</v>
+        <v>100379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         <v>562721</v>
       </c>
       <c r="R5" t="n">
-        <v>6515178</v>
+        <v>6515236</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121500761</v>
+        <v>121501361</v>
       </c>
       <c r="B6" t="n">
         <v>100379</v>
@@ -1126,10 +1126,10 @@
         <v>562721</v>
       </c>
       <c r="R6" t="n">
-        <v>6515236</v>
+        <v>6515178</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501361</v>
+        <v>121501039</v>
       </c>
       <c r="B7" t="n">
-        <v>100379</v>
+        <v>91278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562721</v>
+        <v>562804</v>
       </c>
       <c r="R7" t="n">
-        <v>6515178</v>
+        <v>6515197</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,11 +1304,6 @@
       </c>
       <c r="E8" t="n">
         <v>222498</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,6 +1304,11 @@
       </c>
       <c r="E8" t="n">
         <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122273729</v>
       </c>
       <c r="B8" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501361</v>
+        <v>121500809</v>
       </c>
       <c r="B2" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562721</v>
+        <v>562703</v>
       </c>
       <c r="R2" t="n">
-        <v>6515178</v>
+        <v>6515245</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501108</v>
+        <v>121500891</v>
       </c>
       <c r="B3" t="n">
-        <v>94603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562821</v>
+        <v>562753</v>
       </c>
       <c r="R3" t="n">
-        <v>6515227</v>
+        <v>6515193</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121500891</v>
+        <v>121501108</v>
       </c>
       <c r="B4" t="n">
-        <v>94603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562753</v>
+        <v>562821</v>
       </c>
       <c r="R4" t="n">
-        <v>6515193</v>
+        <v>6515227</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501039</v>
+        <v>121501352</v>
       </c>
       <c r="B5" t="n">
-        <v>91278</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562804</v>
+        <v>562721</v>
       </c>
       <c r="R5" t="n">
-        <v>6515197</v>
+        <v>6515178</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121501352</v>
+        <v>121501039</v>
       </c>
       <c r="B6" t="n">
-        <v>94603</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562721</v>
+        <v>562804</v>
       </c>
       <c r="R6" t="n">
-        <v>6515178</v>
+        <v>6515197</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121500761</v>
+        <v>121500789</v>
       </c>
       <c r="B7" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562721</v>
+        <v>562707</v>
       </c>
       <c r="R7" t="n">
-        <v>6515236</v>
+        <v>6515242</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122273729</v>
+        <v>121500761</v>
       </c>
       <c r="B8" t="n">
-        <v>100507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,17 +1288,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svallberget, Ög</t>
+          <t>Lövkullen, Lövkullen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>562721</v>
       </c>
       <c r="R8" t="n">
-        <v>6515233</v>
+        <v>6515236</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,15 +1342,209 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121501361</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövkullen, Lövkullen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562721</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6515178</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122273729</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svallberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562721</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6515233</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51538-2024 artfynd.xlsx
+++ b/artfynd/A 51538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121500809</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121500891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121501108</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121501352</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121501039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121500789</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121500761</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121501361</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273729</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>